--- a/游戏设计王/老虎机数学入门-PartII-免费游戏RTP模型.xlsx
+++ b/游戏设计王/老虎机数学入门-PartII-免费游戏RTP模型.xlsx
@@ -955,7 +955,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -963,6 +963,7 @@
     <numFmt numFmtId="176" formatCode="0.00000000"/>
     <numFmt numFmtId="177" formatCode="0.0000"/>
     <numFmt numFmtId="178" formatCode="0.0000%"/>
+    <numFmt numFmtId="179" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="37">
     <font>
@@ -1700,7 +1701,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1792,6 +1793,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="179" applyNumberFormat="1" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -7177,7 +7187,7 @@
       <c r="G4" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="51">
         <f>SUM(K68:K98)</f>
         <v>0.6500425</v>
       </c>
@@ -8468,7 +8478,7 @@
         <f t="shared" ref="H68:H98" si="5">PRODUCT(VLOOKUP(C68,$A$53:$F$65,2,FALSE),VLOOKUP(D68,$A$53:$F$65,3,FALSE),VLOOKUP(E68,$A$53:$F$65,4,FALSE),VLOOKUP(F68,$A$53:$F$65,5,FALSE),VLOOKUP(G68,$A$53:$F$65,6,FALSE))</f>
         <v>256</v>
       </c>
-      <c r="I68" s="18">
+      <c r="I68" s="52">
         <f t="shared" ref="I68:I98" si="6">H68/$H$3</f>
         <v>8e-5</v>
       </c>
@@ -8476,7 +8486,7 @@
         <f t="shared" ref="J68:J98" si="7">INDEX($B$4:$D$9,MATCH($A68,$A$4:$A$9,0),MATCH($B68,$B$3:$D$3,0))</f>
         <v>100</v>
       </c>
-      <c r="K68" s="18">
+      <c r="K68" s="52">
         <f t="shared" ref="K68:K98" si="8">I68*J68</f>
         <v>0.008</v>
       </c>
@@ -8507,7 +8517,7 @@
         <f t="shared" si="5"/>
         <v>1024</v>
       </c>
-      <c r="I69" s="18">
+      <c r="I69" s="52">
         <f t="shared" si="6"/>
         <v>0.00032</v>
       </c>
@@ -8515,7 +8525,7 @@
         <f t="shared" si="7"/>
         <v>30</v>
       </c>
-      <c r="K69" s="18">
+      <c r="K69" s="52">
         <f t="shared" si="8"/>
         <v>0.0096</v>
       </c>
@@ -8546,7 +8556,7 @@
         <f t="shared" si="5"/>
         <v>5120</v>
       </c>
-      <c r="I70" s="18">
+      <c r="I70" s="52">
         <f t="shared" si="6"/>
         <v>0.0016</v>
       </c>
@@ -8554,7 +8564,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K70" s="18">
+      <c r="K70" s="52">
         <f t="shared" si="8"/>
         <v>0.008</v>
       </c>
@@ -8585,7 +8595,7 @@
         <f t="shared" si="5"/>
         <v>768</v>
       </c>
-      <c r="I71" s="18">
+      <c r="I71" s="52">
         <f t="shared" si="6"/>
         <v>0.00024</v>
       </c>
@@ -8593,7 +8603,7 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="K71" s="18">
+      <c r="K71" s="52">
         <f t="shared" si="8"/>
         <v>0.024</v>
       </c>
@@ -8624,7 +8634,7 @@
         <f t="shared" si="5"/>
         <v>3072</v>
       </c>
-      <c r="I72" s="18">
+      <c r="I72" s="52">
         <f t="shared" si="6"/>
         <v>0.00096</v>
       </c>
@@ -8632,7 +8642,7 @@
         <f t="shared" si="7"/>
         <v>25</v>
       </c>
-      <c r="K72" s="18">
+      <c r="K72" s="52">
         <f t="shared" si="8"/>
         <v>0.024</v>
       </c>
@@ -8663,7 +8673,7 @@
         <f t="shared" si="5"/>
         <v>15360</v>
       </c>
-      <c r="I73" s="18">
+      <c r="I73" s="52">
         <f t="shared" si="6"/>
         <v>0.0048</v>
       </c>
@@ -8671,7 +8681,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K73" s="18">
+      <c r="K73" s="52">
         <f t="shared" si="8"/>
         <v>0.024</v>
       </c>
@@ -8702,7 +8712,7 @@
         <f t="shared" si="5"/>
         <v>3000</v>
       </c>
-      <c r="I74" s="18">
+      <c r="I74" s="52">
         <f t="shared" si="6"/>
         <v>0.0009375</v>
       </c>
@@ -8710,7 +8720,7 @@
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="K74" s="18">
+      <c r="K74" s="52">
         <f t="shared" si="8"/>
         <v>0.0703125</v>
       </c>
@@ -8741,7 +8751,7 @@
         <f t="shared" si="5"/>
         <v>9000</v>
       </c>
-      <c r="I75" s="18">
+      <c r="I75" s="52">
         <f t="shared" si="6"/>
         <v>0.0028125</v>
       </c>
@@ -8749,7 +8759,7 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="K75" s="18">
+      <c r="K75" s="52">
         <f t="shared" si="8"/>
         <v>0.05625</v>
       </c>
@@ -8780,7 +8790,7 @@
         <f t="shared" si="5"/>
         <v>36000</v>
       </c>
-      <c r="I76" s="18">
+      <c r="I76" s="52">
         <f t="shared" si="6"/>
         <v>0.01125</v>
       </c>
@@ -8788,7 +8798,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K76" s="18">
+      <c r="K76" s="52">
         <f t="shared" si="8"/>
         <v>0.05625</v>
       </c>
@@ -8819,7 +8829,7 @@
         <f t="shared" si="5"/>
         <v>2500</v>
       </c>
-      <c r="I77" s="18">
+      <c r="I77" s="52">
         <f t="shared" si="6"/>
         <v>0.00078125</v>
       </c>
@@ -8827,7 +8837,7 @@
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="K77" s="18">
+      <c r="K77" s="52">
         <f t="shared" si="8"/>
         <v>0.05859375</v>
       </c>
@@ -8858,7 +8868,7 @@
         <f t="shared" si="5"/>
         <v>7500</v>
       </c>
-      <c r="I78" s="18">
+      <c r="I78" s="52">
         <f t="shared" si="6"/>
         <v>0.00234375</v>
       </c>
@@ -8866,7 +8876,7 @@
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
-      <c r="K78" s="18">
+      <c r="K78" s="52">
         <f t="shared" si="8"/>
         <v>0.046875</v>
       </c>
@@ -8897,7 +8907,7 @@
         <f t="shared" si="5"/>
         <v>30000</v>
       </c>
-      <c r="I79" s="18">
+      <c r="I79" s="52">
         <f t="shared" si="6"/>
         <v>0.009375</v>
       </c>
@@ -8905,7 +8915,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K79" s="18">
+      <c r="K79" s="52">
         <f t="shared" si="8"/>
         <v>0.046875</v>
       </c>
@@ -8936,7 +8946,7 @@
         <f t="shared" si="5"/>
         <v>3750</v>
       </c>
-      <c r="I80" s="18">
+      <c r="I80" s="52">
         <f t="shared" si="6"/>
         <v>0.001171875</v>
       </c>
@@ -8944,7 +8954,7 @@
         <f t="shared" si="7"/>
         <v>50</v>
       </c>
-      <c r="K80" s="18">
+      <c r="K80" s="52">
         <f t="shared" si="8"/>
         <v>0.05859375</v>
       </c>
@@ -8975,7 +8985,7 @@
         <f t="shared" si="5"/>
         <v>11250</v>
       </c>
-      <c r="I81" s="18">
+      <c r="I81" s="52">
         <f t="shared" si="6"/>
         <v>0.003515625</v>
       </c>
@@ -8983,7 +8993,7 @@
         <f t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="K81" s="18">
+      <c r="K81" s="52">
         <f t="shared" si="8"/>
         <v>0.03515625</v>
       </c>
@@ -9014,7 +9024,7 @@
         <f t="shared" si="5"/>
         <v>45000</v>
       </c>
-      <c r="I82" s="18">
+      <c r="I82" s="52">
         <f t="shared" si="6"/>
         <v>0.0140625</v>
       </c>
@@ -9022,7 +9032,7 @@
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="K82" s="18">
+      <c r="K82" s="52">
         <f t="shared" si="8"/>
         <v>0.0703125</v>
       </c>
@@ -9053,7 +9063,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I83" s="18">
+      <c r="I83" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9061,7 +9071,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K83" s="18">
+      <c r="K83" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9092,7 +9102,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I84" s="18">
+      <c r="I84" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9100,7 +9110,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K84" s="18">
+      <c r="K84" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9131,7 +9141,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I85" s="18">
+      <c r="I85" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9139,7 +9149,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K85" s="18">
+      <c r="K85" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9170,7 +9180,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I86" s="18">
+      <c r="I86" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9178,7 +9188,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K86" s="18">
+      <c r="K86" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9209,7 +9219,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I87" s="18">
+      <c r="I87" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9217,7 +9227,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K87" s="18">
+      <c r="K87" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9248,7 +9258,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I88" s="18">
+      <c r="I88" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9256,7 +9266,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K88" s="18">
+      <c r="K88" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9287,7 +9297,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I89" s="18">
+      <c r="I89" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9295,7 +9305,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K89" s="18">
+      <c r="K89" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9326,7 +9336,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I90" s="18">
+      <c r="I90" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9334,7 +9344,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K90" s="18">
+      <c r="K90" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9365,7 +9375,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I91" s="18">
+      <c r="I91" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9373,7 +9383,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K91" s="18">
+      <c r="K91" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9404,7 +9414,7 @@
         <f t="shared" si="5"/>
         <v>7803</v>
       </c>
-      <c r="I92" s="18">
+      <c r="I92" s="52">
         <f t="shared" si="6"/>
         <v>0.0024384375</v>
       </c>
@@ -9412,7 +9422,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K92" s="18">
+      <c r="K92" s="52">
         <f t="shared" si="8"/>
         <v>0.004876875</v>
       </c>
@@ -9443,7 +9453,7 @@
         <f t="shared" si="5"/>
         <v>1377</v>
       </c>
-      <c r="I93" s="18">
+      <c r="I93" s="52">
         <f t="shared" si="6"/>
         <v>0.0004303125</v>
       </c>
@@ -9451,7 +9461,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K93" s="18">
+      <c r="K93" s="52">
         <f t="shared" si="8"/>
         <v>0.000860625</v>
       </c>
@@ -9482,7 +9492,7 @@
         <f t="shared" si="5"/>
         <v>1377</v>
       </c>
-      <c r="I94" s="18">
+      <c r="I94" s="52">
         <f t="shared" si="6"/>
         <v>0.0004303125</v>
       </c>
@@ -9490,7 +9500,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K94" s="18">
+      <c r="K94" s="52">
         <f t="shared" si="8"/>
         <v>0.000860625</v>
       </c>
@@ -9521,7 +9531,7 @@
         <f t="shared" si="5"/>
         <v>1377</v>
       </c>
-      <c r="I95" s="18">
+      <c r="I95" s="52">
         <f t="shared" si="6"/>
         <v>0.0004303125</v>
       </c>
@@ -9529,7 +9539,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K95" s="18">
+      <c r="K95" s="52">
         <f t="shared" si="8"/>
         <v>0.000860625</v>
       </c>
@@ -9560,7 +9570,7 @@
         <f t="shared" si="5"/>
         <v>1377</v>
       </c>
-      <c r="I96" s="18">
+      <c r="I96" s="52">
         <f t="shared" si="6"/>
         <v>0.0004303125</v>
       </c>
@@ -9568,7 +9578,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K96" s="18">
+      <c r="K96" s="52">
         <f t="shared" si="8"/>
         <v>0.000860625</v>
       </c>
@@ -9599,7 +9609,7 @@
         <f t="shared" si="5"/>
         <v>1377</v>
       </c>
-      <c r="I97" s="18">
+      <c r="I97" s="52">
         <f t="shared" si="6"/>
         <v>0.0004303125</v>
       </c>
@@ -9607,7 +9617,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K97" s="18">
+      <c r="K97" s="52">
         <f t="shared" si="8"/>
         <v>0.000860625</v>
       </c>
@@ -9638,7 +9648,7 @@
         <f t="shared" si="5"/>
         <v>243</v>
       </c>
-      <c r="I98" s="18">
+      <c r="I98" s="52">
         <f t="shared" si="6"/>
         <v>7.59375e-5</v>
       </c>
@@ -9646,7 +9656,7 @@
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
-      <c r="K98" s="18">
+      <c r="K98" s="52">
         <f t="shared" si="8"/>
         <v>0.000151875</v>
       </c>
@@ -9669,14 +9679,14 @@
         <f>SUM(H68:H98)</f>
         <v>258758</v>
       </c>
-      <c r="I99" s="20">
+      <c r="I99" s="53">
         <f>SUM(I68:I98)</f>
         <v>0.080861875</v>
       </c>
       <c r="J99" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="K99" s="20">
+      <c r="K99" s="53">
         <f>SUM(K68:K98)</f>
         <v>0.6500425</v>
       </c>
@@ -9719,7 +9729,7 @@
       <c r="A103" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B103" s="51">
         <f>SUM(K158:K188)</f>
         <v>1.02276546052632</v>
       </c>
@@ -11110,7 +11120,7 @@
         <f t="shared" ref="H158:H188" si="14">PRODUCT(VLOOKUP(C158,$A$143:$F$155,2,FALSE),VLOOKUP(D158,$A$143:$F$155,3,FALSE),VLOOKUP(E158,$A$143:$F$155,4,FALSE),VLOOKUP(F158,$A$143:$F$155,5,FALSE),VLOOKUP(G158,$A$143:$F$155,6,FALSE))</f>
         <v>625</v>
       </c>
-      <c r="I158" s="18">
+      <c r="I158" s="52">
         <f t="shared" ref="I158:I188" si="15">H158/$B$102</f>
         <v>0.000205592105263158</v>
       </c>
@@ -11118,7 +11128,7 @@
         <f t="shared" ref="J158:J188" si="16">INDEX($B$4:$D$9,MATCH($A158,$A$4:$A$9,0),MATCH($B158,$B$3:$D$3,0))</f>
         <v>100</v>
       </c>
-      <c r="K158" s="18">
+      <c r="K158" s="52">
         <f t="shared" ref="K158:K188" si="17">I158*J158</f>
         <v>0.0205592105263158</v>
       </c>
@@ -11149,7 +11159,7 @@
         <f t="shared" si="14"/>
         <v>1750</v>
       </c>
-      <c r="I159" s="18">
+      <c r="I159" s="52">
         <f t="shared" si="15"/>
         <v>0.000575657894736842</v>
       </c>
@@ -11157,7 +11167,7 @@
         <f t="shared" si="16"/>
         <v>30</v>
       </c>
-      <c r="K159" s="18">
+      <c r="K159" s="52">
         <f t="shared" si="17"/>
         <v>0.0172697368421053</v>
       </c>
@@ -11188,7 +11198,7 @@
         <f t="shared" si="14"/>
         <v>7125</v>
       </c>
-      <c r="I160" s="18">
+      <c r="I160" s="52">
         <f t="shared" si="15"/>
         <v>0.00234375</v>
       </c>
@@ -11196,7 +11206,7 @@
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
-      <c r="K160" s="18">
+      <c r="K160" s="52">
         <f t="shared" si="17"/>
         <v>0.01171875</v>
       </c>
@@ -11227,7 +11237,7 @@
         <f t="shared" si="14"/>
         <v>768</v>
       </c>
-      <c r="I161" s="18">
+      <c r="I161" s="52">
         <f t="shared" si="15"/>
         <v>0.000252631578947368</v>
       </c>
@@ -11235,7 +11245,7 @@
         <f t="shared" si="16"/>
         <v>100</v>
       </c>
-      <c r="K161" s="18">
+      <c r="K161" s="52">
         <f t="shared" si="17"/>
         <v>0.0252631578947368</v>
       </c>
@@ -11266,7 +11276,7 @@
         <f t="shared" si="14"/>
         <v>2880</v>
       </c>
-      <c r="I162" s="18">
+      <c r="I162" s="52">
         <f t="shared" si="15"/>
         <v>0.000947368421052632</v>
       </c>
@@ -11274,7 +11284,7 @@
         <f t="shared" si="16"/>
         <v>25</v>
       </c>
-      <c r="K162" s="18">
+      <c r="K162" s="52">
         <f t="shared" si="17"/>
         <v>0.0236842105263158</v>
       </c>
@@ -11305,7 +11315,7 @@
         <f t="shared" si="14"/>
         <v>14592</v>
       </c>
-      <c r="I163" s="18">
+      <c r="I163" s="52">
         <f t="shared" si="15"/>
         <v>0.0048</v>
       </c>
@@ -11313,7 +11323,7 @@
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
-      <c r="K163" s="18">
+      <c r="K163" s="52">
         <f t="shared" si="17"/>
         <v>0.024</v>
       </c>
@@ -11344,7 +11354,7 @@
         <f t="shared" si="14"/>
         <v>6048</v>
       </c>
-      <c r="I164" s="18">
+      <c r="I164" s="52">
         <f t="shared" si="15"/>
         <v>0.00198947368421053</v>
       </c>
@@ -11352,7 +11362,7 @@
         <f t="shared" si="16"/>
         <v>75</v>
       </c>
-      <c r="K164" s="18">
+      <c r="K164" s="52">
         <f t="shared" si="17"/>
         <v>0.149210526315789</v>
       </c>
@@ -11383,7 +11393,7 @@
         <f t="shared" si="14"/>
         <v>13104</v>
       </c>
-      <c r="I165" s="18">
+      <c r="I165" s="52">
         <f t="shared" si="15"/>
         <v>0.00431052631578947</v>
       </c>
@@ -11391,7 +11401,7 @@
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
-      <c r="K165" s="18">
+      <c r="K165" s="52">
         <f t="shared" si="17"/>
         <v>0.0862105263157895</v>
       </c>
@@ -11422,7 +11432,7 @@
         <f t="shared" si="14"/>
         <v>44688</v>
       </c>
-      <c r="I166" s="18">
+      <c r="I166" s="52">
         <f t="shared" si="15"/>
         <v>0.0147</v>
       </c>
@@ -11430,7 +11440,7 @@
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
-      <c r="K166" s="18">
+      <c r="K166" s="52">
         <f t="shared" si="17"/>
         <v>0.0735</v>
       </c>
@@ -11461,7 +11471,7 @@
         <f t="shared" si="14"/>
         <v>5400</v>
       </c>
-      <c r="I167" s="18">
+      <c r="I167" s="52">
         <f t="shared" si="15"/>
         <v>0.00177631578947368</v>
       </c>
@@ -11469,7 +11479,7 @@
         <f t="shared" si="16"/>
         <v>75</v>
       </c>
-      <c r="K167" s="18">
+      <c r="K167" s="52">
         <f t="shared" si="17"/>
         <v>0.133223684210526</v>
       </c>
@@ -11500,7 +11510,7 @@
         <f t="shared" si="14"/>
         <v>11700</v>
       </c>
-      <c r="I168" s="18">
+      <c r="I168" s="52">
         <f t="shared" si="15"/>
         <v>0.00384868421052632</v>
       </c>
@@ -11508,7 +11518,7 @@
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
-      <c r="K168" s="18">
+      <c r="K168" s="52">
         <f t="shared" si="17"/>
         <v>0.0769736842105263</v>
       </c>
@@ -11539,7 +11549,7 @@
         <f t="shared" si="14"/>
         <v>39900</v>
       </c>
-      <c r="I169" s="18">
+      <c r="I169" s="52">
         <f t="shared" si="15"/>
         <v>0.013125</v>
       </c>
@@ -11547,7 +11557,7 @@
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
-      <c r="K169" s="18">
+      <c r="K169" s="52">
         <f t="shared" si="17"/>
         <v>0.065625</v>
       </c>
@@ -11578,7 +11588,7 @@
         <f t="shared" si="14"/>
         <v>6480</v>
       </c>
-      <c r="I170" s="18">
+      <c r="I170" s="52">
         <f t="shared" si="15"/>
         <v>0.00213157894736842</v>
       </c>
@@ -11586,7 +11596,7 @@
         <f t="shared" si="16"/>
         <v>50</v>
       </c>
-      <c r="K170" s="18">
+      <c r="K170" s="52">
         <f t="shared" si="17"/>
         <v>0.106578947368421</v>
       </c>
@@ -11617,7 +11627,7 @@
         <f t="shared" si="14"/>
         <v>18144</v>
       </c>
-      <c r="I171" s="18">
+      <c r="I171" s="52">
         <f t="shared" si="15"/>
         <v>0.00596842105263158</v>
       </c>
@@ -11625,7 +11635,7 @@
         <f t="shared" si="16"/>
         <v>10</v>
       </c>
-      <c r="K171" s="18">
+      <c r="K171" s="52">
         <f t="shared" si="17"/>
         <v>0.0596842105263158</v>
       </c>
@@ -11656,7 +11666,7 @@
         <f t="shared" si="14"/>
         <v>57456</v>
       </c>
-      <c r="I172" s="18">
+      <c r="I172" s="52">
         <f t="shared" si="15"/>
         <v>0.0189</v>
       </c>
@@ -11664,7 +11674,7 @@
         <f t="shared" si="16"/>
         <v>5</v>
       </c>
-      <c r="K172" s="18">
+      <c r="K172" s="52">
         <f t="shared" si="17"/>
         <v>0.0945</v>
       </c>
@@ -11695,7 +11705,7 @@
         <f t="shared" si="14"/>
         <v>7344</v>
       </c>
-      <c r="I173" s="18">
+      <c r="I173" s="52">
         <f t="shared" si="15"/>
         <v>0.00241578947368421</v>
       </c>
@@ -11703,7 +11713,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K173" s="18">
+      <c r="K173" s="52">
         <f t="shared" si="17"/>
         <v>0.00483157894736842</v>
       </c>
@@ -11734,7 +11744,7 @@
         <f t="shared" si="14"/>
         <v>7344</v>
       </c>
-      <c r="I174" s="18">
+      <c r="I174" s="52">
         <f t="shared" si="15"/>
         <v>0.00241578947368421</v>
       </c>
@@ -11742,7 +11752,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K174" s="18">
+      <c r="K174" s="52">
         <f t="shared" si="17"/>
         <v>0.00483157894736842</v>
       </c>
@@ -11773,7 +11783,7 @@
         <f t="shared" si="14"/>
         <v>7803</v>
       </c>
-      <c r="I175" s="18">
+      <c r="I175" s="52">
         <f t="shared" si="15"/>
         <v>0.00256677631578947</v>
       </c>
@@ -11781,7 +11791,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K175" s="18">
+      <c r="K175" s="52">
         <f t="shared" si="17"/>
         <v>0.00513355263157895</v>
       </c>
@@ -11812,7 +11822,7 @@
         <f t="shared" si="14"/>
         <v>7344</v>
       </c>
-      <c r="I176" s="18">
+      <c r="I176" s="52">
         <f t="shared" si="15"/>
         <v>0.00241578947368421</v>
       </c>
@@ -11820,7 +11830,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K176" s="18">
+      <c r="K176" s="52">
         <f t="shared" si="17"/>
         <v>0.00483157894736842</v>
       </c>
@@ -11851,7 +11861,7 @@
         <f t="shared" si="14"/>
         <v>7803</v>
       </c>
-      <c r="I177" s="18">
+      <c r="I177" s="52">
         <f t="shared" si="15"/>
         <v>0.00256677631578947</v>
       </c>
@@ -11859,7 +11869,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K177" s="18">
+      <c r="K177" s="52">
         <f t="shared" si="17"/>
         <v>0.00513355263157895</v>
       </c>
@@ -11890,7 +11900,7 @@
         <f t="shared" si="14"/>
         <v>7803</v>
       </c>
-      <c r="I178" s="18">
+      <c r="I178" s="52">
         <f t="shared" si="15"/>
         <v>0.00256677631578947</v>
       </c>
@@ -11898,7 +11908,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K178" s="18">
+      <c r="K178" s="52">
         <f t="shared" si="17"/>
         <v>0.00513355263157895</v>
       </c>
@@ -11929,7 +11939,7 @@
         <f t="shared" si="14"/>
         <v>7344</v>
       </c>
-      <c r="I179" s="18">
+      <c r="I179" s="52">
         <f t="shared" si="15"/>
         <v>0.00241578947368421</v>
       </c>
@@ -11937,7 +11947,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K179" s="18">
+      <c r="K179" s="52">
         <f t="shared" si="17"/>
         <v>0.00483157894736842</v>
       </c>
@@ -11968,7 +11978,7 @@
         <f t="shared" si="14"/>
         <v>7803</v>
       </c>
-      <c r="I180" s="18">
+      <c r="I180" s="52">
         <f t="shared" si="15"/>
         <v>0.00256677631578947</v>
       </c>
@@ -11976,7 +11986,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K180" s="18">
+      <c r="K180" s="52">
         <f t="shared" si="17"/>
         <v>0.00513355263157895</v>
       </c>
@@ -12007,7 +12017,7 @@
         <f t="shared" si="14"/>
         <v>7803</v>
       </c>
-      <c r="I181" s="18">
+      <c r="I181" s="52">
         <f t="shared" si="15"/>
         <v>0.00256677631578947</v>
       </c>
@@ -12015,7 +12025,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K181" s="18">
+      <c r="K181" s="52">
         <f t="shared" si="17"/>
         <v>0.00513355263157895</v>
       </c>
@@ -12046,7 +12056,7 @@
         <f t="shared" si="14"/>
         <v>7803</v>
       </c>
-      <c r="I182" s="18">
+      <c r="I182" s="52">
         <f t="shared" si="15"/>
         <v>0.00256677631578947</v>
       </c>
@@ -12054,7 +12064,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K182" s="18">
+      <c r="K182" s="52">
         <f t="shared" si="17"/>
         <v>0.00513355263157895</v>
       </c>
@@ -12085,7 +12095,7 @@
         <f t="shared" si="14"/>
         <v>1296</v>
       </c>
-      <c r="I183" s="18">
+      <c r="I183" s="52">
         <f t="shared" si="15"/>
         <v>0.000426315789473684</v>
       </c>
@@ -12093,7 +12103,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K183" s="18">
+      <c r="K183" s="52">
         <f t="shared" si="17"/>
         <v>0.000852631578947368</v>
       </c>
@@ -12124,7 +12134,7 @@
         <f t="shared" si="14"/>
         <v>1377</v>
       </c>
-      <c r="I184" s="18">
+      <c r="I184" s="52">
         <f t="shared" si="15"/>
         <v>0.000452960526315789</v>
       </c>
@@ -12132,7 +12142,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K184" s="18">
+      <c r="K184" s="52">
         <f t="shared" si="17"/>
         <v>0.000905921052631579</v>
       </c>
@@ -12163,7 +12173,7 @@
         <f t="shared" si="14"/>
         <v>1377</v>
       </c>
-      <c r="I185" s="18">
+      <c r="I185" s="52">
         <f t="shared" si="15"/>
         <v>0.000452960526315789</v>
       </c>
@@ -12171,7 +12181,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K185" s="18">
+      <c r="K185" s="52">
         <f t="shared" si="17"/>
         <v>0.000905921052631579</v>
       </c>
@@ -12202,7 +12212,7 @@
         <f t="shared" si="14"/>
         <v>1377</v>
       </c>
-      <c r="I186" s="18">
+      <c r="I186" s="52">
         <f t="shared" si="15"/>
         <v>0.000452960526315789</v>
       </c>
@@ -12210,7 +12220,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K186" s="18">
+      <c r="K186" s="52">
         <f t="shared" si="17"/>
         <v>0.000905921052631579</v>
       </c>
@@ -12241,7 +12251,7 @@
         <f t="shared" si="14"/>
         <v>1377</v>
       </c>
-      <c r="I187" s="18">
+      <c r="I187" s="52">
         <f t="shared" si="15"/>
         <v>0.000452960526315789</v>
       </c>
@@ -12249,7 +12259,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K187" s="18">
+      <c r="K187" s="52">
         <f t="shared" si="17"/>
         <v>0.000905921052631579</v>
       </c>
@@ -12280,7 +12290,7 @@
         <f t="shared" si="14"/>
         <v>243</v>
       </c>
-      <c r="I188" s="18">
+      <c r="I188" s="52">
         <f t="shared" si="15"/>
         <v>7.99342105263158e-5</v>
       </c>
@@ -12288,7 +12298,7 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="K188" s="18">
+      <c r="K188" s="52">
         <f t="shared" si="17"/>
         <v>0.000159868421052632</v>
       </c>
@@ -12319,14 +12329,14 @@
         <f>SUM(H158:H188)</f>
         <v>313901</v>
       </c>
-      <c r="I189" s="20">
+      <c r="I189" s="53">
         <f>SUM(I158:I188)</f>
         <v>0.103256907894737</v>
       </c>
       <c r="J189" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="K189" s="20">
+      <c r="K189" s="53">
         <f>SUM(K158:K188)</f>
         <v>1.02276546052632</v>
       </c>
@@ -12401,7 +12411,7 @@
       <c r="A196" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B196" s="22">
+      <c r="B196" s="54">
         <f>$H$4</f>
         <v>0.6500425</v>
       </c>
@@ -12413,7 +12423,7 @@
       <c r="A197" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="B197" s="18">
+      <c r="B197" s="52">
         <f>SUMIFS($I$68:$I$98,$A$68:$A$98,"S",$B$68:$B$98,3)</f>
         <v>0.024384375</v>
       </c>
@@ -12425,7 +12435,7 @@
       <c r="A198" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B198" s="18">
+      <c r="B198" s="52">
         <f>SUMIFS($I$68:$I$98,$A$68:$A$98,"S",$B$68:$B$98,4)</f>
         <v>0.0021515625</v>
       </c>
@@ -12437,7 +12447,7 @@
       <c r="A199" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B199" s="18">
+      <c r="B199" s="52">
         <f>SUMIFS($I$68:$I$98,$A$68:$A$98,"S",$B$68:$B$98,5)</f>
         <v>7.59375e-5</v>
       </c>
@@ -12507,7 +12517,7 @@
       <c r="A205" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B205" s="22">
+      <c r="B205" s="54">
         <f>$B$103</f>
         <v>1.02276546052632</v>
       </c>
@@ -12519,7 +12529,7 @@
       <c r="A206" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="B206" s="18">
+      <c r="B206" s="52">
         <f>SUMIFS($I$158:$I$188,$A$158:$A$188,"S",$B$158:$B$188,3)</f>
         <v>0.0250638157894737</v>
       </c>
@@ -12531,7 +12541,7 @@
       <c r="A207" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B207" s="18">
+      <c r="B207" s="52">
         <f>SUMIFS($I$158:$I$188,$A$158:$A$188,"S",$B$158:$B$188,4)</f>
         <v>0.00223815789473684</v>
       </c>
@@ -12543,7 +12553,7 @@
       <c r="A208" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B208" s="18">
+      <c r="B208" s="52">
         <f>SUMIFS($I$158:$I$188,$A$158:$A$188,"S",$B$158:$B$188,5)</f>
         <v>7.99342105263158e-5</v>
       </c>
@@ -12636,7 +12646,7 @@
       <c r="A216" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B216" s="18">
+      <c r="B216" s="52">
         <f>B197*$B$205*B213</f>
         <v>0.349199358128103</v>
       </c>
@@ -12648,7 +12658,7 @@
       <c r="A217" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="B217" s="18">
+      <c r="B217" s="52">
         <f>B198*$B$205*B214</f>
         <v>0.0462175621051902</v>
       </c>
@@ -12660,7 +12670,7 @@
       <c r="A218" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B218" s="18">
+      <c r="B218" s="52">
         <f>B199*$B$205*B215</f>
         <v>0.00217494409906777</v>
       </c>
@@ -12672,7 +12682,7 @@
       <c r="A219" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="B219" s="10">
+      <c r="B219" s="51">
         <f>SUM(B216:B218)</f>
         <v>0.397591864332361</v>
       </c>
@@ -12706,7 +12716,7 @@
       <c r="A222" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B222" s="22">
+      <c r="B222" s="54">
         <f>B196+B219</f>
         <v>1.04763436433236</v>
       </c>
@@ -12795,7 +12805,7 @@
       <c r="A230" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="B230" s="18">
+      <c r="B230" s="52">
         <f>B222-(B225+B228)</f>
         <v>3.43643323610365e-5</v>
       </c>
